--- a/DATA/production_capacity_scenarios/production_capacity_scenarios.xlsx
+++ b/DATA/production_capacity_scenarios/production_capacity_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_9D1BB44975AAC4FDB29A4B1CF35106638C1C9F0C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AFF4C07-39BE-489C-8AD5-4D07DCDC7BA2}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_9D1BB44975AAC4FDB29A4B1CF35106638C1C9F0C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0597B556-6936-4D0B-AFC2-EA98178D2014}"/>
   <bookViews>
     <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,20 @@
     <sheet name="other" sheetId="13" r:id="rId13"/>
     <sheet name="other_scaled" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -137,11 +150,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -157,6 +171,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,10 +462,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -489,34 +508,34 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>7711003</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>7711003</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>7711003</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>7711003</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>7711003</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>7711003</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>7711003</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7711003</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>7711003</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>7711003</v>
       </c>
     </row>
@@ -524,34 +543,34 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>39223956</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>39223956</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>39223956</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>39223956</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>39223956</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>39223956</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>39223956</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>39223956</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>39223956</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>39223956</v>
       </c>
     </row>
@@ -559,34 +578,34 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>61029105</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>61029105</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>61029105</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>61029105</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>61029105</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>61029105</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>61029105</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>61029105</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>61029105</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>61029105</v>
       </c>
     </row>
@@ -594,34 +613,34 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>12048153</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>12048153</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>12048153</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>12048153</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>12048153</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>12048153</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>12048153</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>12048153</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>12048153</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>12048153</v>
       </c>
     </row>
@@ -629,34 +648,34 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>164885690</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>164885690</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>164885690</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>164885690</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>164885690</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>164885690</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>164885690</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>164885690</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>164885690</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>164885690</v>
       </c>
     </row>
@@ -664,34 +683,34 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>12812242</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>12812242</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>12812242</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>12812242</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>12812242</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>12812242</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>12812242</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>12812242</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>12812242</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>12812242</v>
       </c>
     </row>
@@ -699,34 +718,34 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>226762686</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>226762686</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>226762686</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>226762686</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>226762686</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>226762686</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>226762686</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>226762686</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>226762686</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>226762686</v>
       </c>
     </row>
@@ -734,34 +753,34 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>80972855</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>80972855</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>80972855</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>80972855</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>80972855</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>80972855</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>80972855</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>80972855</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>80972855</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>80972855</v>
       </c>
     </row>
@@ -769,34 +788,34 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>43702188</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>43702188</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>43702188</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>43702188</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>43702188</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>43702188</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>43702188</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>43702188</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>43702188</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>43702188</v>
       </c>
     </row>
@@ -804,34 +823,34 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>56991052</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>56991052</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>56991052</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>56991052</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>56991052</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>56991052</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>56991052</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>56991052</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>56991052</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="2">
         <v>56991052</v>
       </c>
     </row>
@@ -839,34 +858,34 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>45911731</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>45911731</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>45911731</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>45911731</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>45911731</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>45911731</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>45911731</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>45911731</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>45911731</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>45911731</v>
       </c>
     </row>
@@ -874,34 +893,34 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>10874165</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>10874165</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>10874165</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>10874165</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>10874165</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>10874165</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>10874165</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>10874165</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>10874165</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>10874165</v>
       </c>
     </row>
@@ -909,34 +928,34 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>83916974</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>83916974</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>83916974</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>83916974</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>83916974</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>83916974</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>83916974</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>83916974</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>83916974</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>83916974</v>
       </c>
     </row>
@@ -944,34 +963,34 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>87429432</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>87429432</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>87429432</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>87429432</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>87429432</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>87429432</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>87429432</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>87429432</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>87429432</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>87429432</v>
       </c>
     </row>
@@ -979,35 +998,41 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>587114096</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>587114096</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>587114096</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>587114096</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>587114096</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>587114096</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>587114096</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>587114096</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="2">
         <v>587114096</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="2">
         <v>587114096</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="2">
+        <f>B16*1.5</f>
+        <v>880671144</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/production_capacity_scenarios/production_capacity_scenarios.xlsx
+++ b/DATA/production_capacity_scenarios/production_capacity_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_9D1BB44975AAC4FDB29A4B1CF35106638C1C9F0C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0597B556-6936-4D0B-AFC2-EA98178D2014}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{660A6D66-C27E-40E3-8B10-8476F2467E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="master_capacity" sheetId="1" r:id="rId1"/>
@@ -171,10 +171,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1030,10 +1026,7 @@
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="2">
-        <f>B16*1.5</f>
-        <v>880671144</v>
-      </c>
+      <c r="B17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DATA/production_capacity_scenarios/production_capacity_scenarios.xlsx
+++ b/DATA/production_capacity_scenarios/production_capacity_scenarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{660A6D66-C27E-40E3-8B10-8476F2467E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{660A6D66-C27E-40E3-8B10-8476F2467E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F09BEBD-4AD2-4CA2-AB5B-DB5266C0FBBF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,6 +28,9 @@
     <sheet name="other" sheetId="13" r:id="rId13"/>
     <sheet name="other_scaled" sheetId="14" r:id="rId14"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">master_capacity!$A$1:$B$17</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -115,12 +118,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -150,12 +159,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -462,7 +472,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -852,10 +862,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>45911731</v>
+        <v>10874165</v>
       </c>
       <c r="C12" s="2">
         <v>45911731</v>
@@ -887,10 +897,10 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>10874165</v>
+        <v>83916974</v>
       </c>
       <c r="C13" s="2">
         <v>10874165</v>
@@ -922,10 +932,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2">
-        <v>83916974</v>
+        <v>45911731</v>
       </c>
       <c r="C14" s="2">
         <v>83916974</v>
@@ -1029,6 +1039,11 @@
       <c r="B17" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B17" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B17">
+      <sortCondition ref="A1:A17"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5027,6 +5042,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -5063,38 +5081,38 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>7711003</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>7711003</v>
       </c>
-      <c r="D2">
-        <v>7094122</v>
-      </c>
-      <c r="E2">
-        <v>6939902</v>
-      </c>
-      <c r="F2">
-        <v>7479673</v>
-      </c>
-      <c r="G2">
+      <c r="D2" s="3">
         <v>7711003</v>
       </c>
-      <c r="H2">
+      <c r="E2" s="3">
         <v>7711003</v>
       </c>
-      <c r="I2">
+      <c r="F2" s="3">
         <v>7711003</v>
       </c>
-      <c r="J2">
+      <c r="G2" s="3">
         <v>7711003</v>
       </c>
-      <c r="K2">
+      <c r="H2" s="3">
+        <v>7711003</v>
+      </c>
+      <c r="I2" s="3">
+        <v>7711003</v>
+      </c>
+      <c r="J2" s="3">
+        <v>7711003</v>
+      </c>
+      <c r="K2" s="3">
         <v>7711003</v>
       </c>
     </row>
@@ -5168,38 +5186,38 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>12048153</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>12048153</v>
       </c>
-      <c r="D5">
-        <v>11084301</v>
-      </c>
-      <c r="E5">
-        <v>10843338</v>
-      </c>
-      <c r="F5">
-        <v>11686709</v>
-      </c>
-      <c r="G5">
+      <c r="D5" s="3">
+        <v>11014301</v>
+      </c>
+      <c r="E5" s="3">
+        <v>10343338</v>
+      </c>
+      <c r="F5" s="3">
+        <v>11286709</v>
+      </c>
+      <c r="G5" s="3">
         <v>12048153</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <v>12048153</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="3">
         <v>12048153</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="3">
         <v>12048153</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="3">
         <v>12048153</v>
       </c>
     </row>
@@ -5343,38 +5361,38 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>43702188</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="3">
         <v>43702188</v>
       </c>
-      <c r="D10">
-        <v>43493336</v>
-      </c>
-      <c r="E10">
-        <v>43441123</v>
-      </c>
-      <c r="F10">
-        <v>43623868</v>
-      </c>
-      <c r="G10">
+      <c r="D10" s="3">
         <v>43702188</v>
       </c>
-      <c r="H10">
+      <c r="E10" s="3">
         <v>43702188</v>
       </c>
-      <c r="I10">
+      <c r="F10" s="3">
         <v>43702188</v>
       </c>
-      <c r="J10">
+      <c r="G10" s="3">
         <v>43702188</v>
       </c>
-      <c r="K10">
+      <c r="H10" s="3">
+        <v>43702188</v>
+      </c>
+      <c r="I10" s="3">
+        <v>43702188</v>
+      </c>
+      <c r="J10" s="3">
+        <v>43702188</v>
+      </c>
+      <c r="K10" s="3">
         <v>43702188</v>
       </c>
     </row>
@@ -5518,38 +5536,38 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="3">
         <v>87429432</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="3">
         <v>87429432</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="3">
         <v>82259017</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="3">
         <v>80966413</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="3">
         <v>85490526</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="3">
         <v>87429432</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="3">
         <v>87429432</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="3">
         <v>87429432</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="3">
         <v>87429432</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="3">
         <v>87429432</v>
       </c>
     </row>
